--- a/artfynd/A 53021-2022 artfynd.xlsx
+++ b/artfynd/A 53021-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53021-2022 artfynd.xlsx
+++ b/artfynd/A 53021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103995757</v>
+        <v>104044279</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäckedalsbäcken, Jmt</t>
+          <t>Tångarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551200.683942266</v>
+        <v>551203</v>
       </c>
       <c r="R2" t="n">
-        <v>7014710.553343374</v>
+        <v>7014419</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-07-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-07-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:04</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,40 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>103997346</v>
       </c>
       <c r="B3" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>551197.4056123943</v>
+        <v>551197</v>
       </c>
       <c r="R3" t="n">
-        <v>7014661.400659107</v>
+        <v>7014662</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,50 +888,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103997398</v>
+        <v>104044281</v>
       </c>
       <c r="B4" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bäckedalsbäcken, Jmt</t>
+          <t>Tångarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551209.6614674545</v>
+        <v>551193</v>
       </c>
       <c r="R4" t="n">
-        <v>7014457.977832013</v>
+        <v>7014382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,22 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-07-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-07-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2022-10-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,40 +969,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104044279</v>
+        <v>103997398</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,34 +996,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tångarna, Jmt</t>
+          <t>Bäckedalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551203.5194064295</v>
+        <v>551210</v>
       </c>
       <c r="R5" t="n">
-        <v>7014418.686818101</v>
+        <v>7014458</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,22 +1050,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,31 +1076,35 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104044280</v>
+        <v>103997377</v>
       </c>
       <c r="B6" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,34 +1112,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tångarna, Jmt</t>
+          <t>Bäckedalsbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551210.9503785153</v>
+        <v>551169</v>
       </c>
       <c r="R6" t="n">
-        <v>7014376.908067957</v>
+        <v>7014726</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1220,22 +1166,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-03</t>
+          <t>2022-07-20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,53 +1192,57 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104044281</v>
+        <v>104044280</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551192.8313192793</v>
+        <v>551211</v>
       </c>
       <c r="R7" t="n">
-        <v>7014381.575622248</v>
+        <v>7014377</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,19 +1285,9 @@
           <t>2022-10-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,6 +1311,122 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>103997427</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100143</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222467</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gräsull</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eriophorum latifolium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Hoppe</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bäckedalsbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>551162</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7014733</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-07-20</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-07-20</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53021-2022 artfynd.xlsx
+++ b/artfynd/A 53021-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044279</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997346</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044281</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997398</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997377</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1311,6 +1341,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104044280</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,8 +1462,22 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997427</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>